--- a/config.xlsx
+++ b/config.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t xml:space="preserve">01e7c268d5cd4e05f035609cd6a7302bba559e0e32730b03d62eee6dcd144f3e</t>
+    <t xml:space="preserve">02d45b28f76a0457b099d10f690607a3ed53295b69fd2fb38eb57af9533598be</t>
   </si>
 </sst>
 </file>
